--- a/Configs/GameConfig/Datas/fg/#BuildingFluidPort-建筑流体端口.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingFluidPort-建筑流体端口.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,6 +780,40 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>fuel_generator.fin0</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>fuel_generator</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildingFluidPort-建筑流体端口.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingFluidPort-建筑流体端口.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -814,6 +814,40 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>purifier.fin0</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>coolant</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
